--- a/proposal/创智汇30场活动方案排期表.xlsx
+++ b/proposal/创智汇30场活动方案排期表.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30场总表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="协同与闭环" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30场总表-WAIC对齐" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WAIC议程映射" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WAICA学术日程摘要" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,7 +38,23 @@
     </font>
     <font>
       <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
       <color rgb="002C2C2C"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -70,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -82,6 +99,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -449,23 +475,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:M31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -476,12 +501,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>主题代码</t>
+          <t>主题</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>主题类型</t>
+          <t>WAIC赛道</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -491,7 +516,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>建议档期</t>
+          <t>档期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -516,7 +541,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>行程要点</t>
+          <t>行程</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -531,32 +556,27 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>现场人力</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>逼单要点</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="48" customHeight="1">
+          <t>人力</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="50" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>智能体/多模态/算力训练</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AI培训 / 黑客松</t>
+          <t>智能伙伴</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>创智汇·AI工具链上手营</t>
+          <t>智能伙伴·创智汇开年主题沙龙</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -566,67 +586,62 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>3F培训/OPC</t>
+          <t>5F沙龙</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>半天（13:30–17:30）</t>
+          <t>2.5小时</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>工作坊+看场</t>
+          <t>主题沙龙</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>AI讲师×1、园区政策专员×1</t>
+          <t>联合会领导、AI企业代表、服务中心</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>13:30 签到参观样板间 / 14:00 开场+空间政策礼包 / 14:30 工具链实操 / 16:30 工位/单元看场 / 17:00 意向登记逼单</t>
+          <t>18:30 签到参观 / 19:00 WAIC主题年度解读 / 19:30 园区AI+内容定位发布 / 20:10 圆桌：智能伙伴如何落杨浦 / 20:40 看场+意向</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>OPC社群体验、载体活跃度、培训KPI</t>
+          <t>把WAIC年度主题转化为园区主叙事</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>引流AI初创，当场看场转化</t>
+          <t>开年集中获客与品牌定调</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>我方3+园区2</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
+          <t>我方3+园区2+联合会1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="50" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>智能体/多模态/算力训练</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>AI培训 / 黑客松</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>AIGC内容生产实战工作坊</t>
+          <t>Agent智能体搭建一日营</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -636,7 +651,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>3F直播间+培训</t>
+          <t>3F OPC</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -651,52 +666,47 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>AIGC创作者、内容机构导师</t>
+          <t>Agent工程师、开源Maintainer</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>09:30 签到 / 10:00 案例拆解 / 13:30 实操产出 / 16:00 优秀作品路演 / 16:40 入驻政策+看场</t>
+          <t>09:30 签到 / 10:00 Agent工作流拆解 / 13:30 低代码实操（对齐MCP工具调用） / 16:00 Demo路演 / 16:40 看场逼单</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>内容氛围、直播间利用率</t>
+          <t>对齐WAICA Agent/工具评测赛道</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>锁定内容型租户与联合办公需求</t>
+          <t>Agent初创工位/单元转化</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>我方4+园区2</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="48" customHeight="1">
+          <t>我方3+园区2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="50" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>智能体/多模态/算力训练</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AI培训 / 黑客松</t>
+          <t>多模态</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>OPC超级个体黑客松（春季）</t>
+          <t>多模态智能体工作坊</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -706,67 +716,62 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3F整层开放</t>
+          <t>3F培训+直播间</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1.5天</t>
+          <t>1天</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>黑客松</t>
+          <t>工作坊</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>技术评委×3、投资人×2、云厂商</t>
+          <t>多模态研究者、应用厂商</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>D1 组队开题 / D1夜 封闭开发 / D2路演决赛 / 颁奖+入驻礼包发布 / 一对一看场</t>
+          <t>多模态案例 / 视觉-语言实操 / 行业场景共创 / 作品评审 / 政策礼包+看场</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>品牌声量、媒体曝光、青年人才黏性</t>
+          <t>承接WAICA「科学多模态智能体」议题落地</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>获奖团队优先谈单元/工位</t>
+          <t>多模态应用团队入驻</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>我方5+园区3</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="48" customHeight="1">
+          <t>我方4+园区2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="50" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>智能体/多模态/算力训练</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>AI培训 / 黑客松</t>
+          <t>算力Infra</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>数字人直播实训营</t>
+          <t>火山引擎×算力Infra实务营</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -776,137 +781,127 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>3F直播间</t>
+          <t>3F+云创基地</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>半天</t>
+          <t>1天</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>实训+演示</t>
+          <t>厂商联训</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>数字人厂商、直播操盘手</t>
+          <t>火山引擎讲师、云计算创新基地</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>参观直播间 / 数字人搭建演示 / 跟播实操 / 商业变现路径 / 空间与套餐报价</t>
+          <t>算力政策包 / 代金券/折扣实操 / 集群调度案例（呼应WAIC Infra） / 一对一诊断 / 入驻捆绑云资源</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>直播间运营样板</t>
+          <t>国级孵化器+专有算力包兑现</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>直播/MCN类客户转化</t>
+          <t>高算力消耗型企业定向招商</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>我方3+园区2</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1">
+          <t>我方3+园区2+厂商2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="50" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>智能体/多模态/算力训练</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>AI培训 / 黑客松</t>
+          <t>具身智能</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>火山引擎·算力应用训练营</t>
+          <t>具身智能空间交互体验日</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4月中旬</t>
+          <t>4月上旬</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3F+云创协同</t>
+          <t>5F展区角+3F</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1天</t>
+          <t>半天</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>厂商联训</t>
+          <t>体验日</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>火山引擎讲师、算力政策专员</t>
+          <t>机器人/具身团队、高校实验室</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>算力政策包解读 / 代金券/折扣实操 / 企业案例 / 一对一算力诊断 / 入驻+云资源捆绑报价</t>
+          <t>具身演示 / 空间交互讲解 / 场景清单对接 / 5F应用场景踩点 / 落位洽谈</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>专有算力政策兑现、云基地协同</t>
+          <t>对齐WAICA具身智能空间交互工作坊</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>AI算力消耗型企业定向招商</t>
+          <t>具身/机器人团队看场</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>我方3+园区2+厂商2</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1">
+          <t>我方3+园区2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="50" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>智能体/多模态/算力训练</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>AI培训 / 黑客松</t>
+          <t>AI内容</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>AI微短剧脚本与制作特训</t>
+          <t>AIGC微短剧制片特训</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -916,7 +911,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>5F展厅角+3F</t>
+          <t>3F直播间+5F</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -931,22 +926,22 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>微短剧导演/编剧、平台方</t>
+          <t>微短剧导演、平台方</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>政策与集聚区解读 / 脚本工作坊 / AIGC制片流程 / 优秀剧本路演 / 5F场景踩点</t>
+          <t>YOUNG立方政策 / AIGC制片流程 / 脚本工作坊 / 优秀作品路演 / 5F场景看场</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>对齐YOUNG立方/微短剧定位</t>
+          <t>内容赛道+官方创作者夜场错位协同</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>厂牌/工作室看场5F或3F</t>
+          <t>厂牌/工作室入驻</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -954,389 +949,359 @@
           <t>我方4+园区2</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1">
+    </row>
+    <row r="8" ht="50" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>智能体/多模态/算力训练</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>AI培训 / 黑客松</t>
+          <t>Builders</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>智能体搭建一日营</t>
+          <t>OPC超级个体黑客松（春）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6月中旬</t>
+          <t>5月中旬</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3F OPC</t>
+          <t>3F整层</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1天</t>
+          <t>1.5天</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>一日营</t>
+          <t>黑客松</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>智能体工程师、行业顾问</t>
+          <t>评委×3、投资人×2、云厂商</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>需求拆解 / 低代码搭建 / 行业垂类案例 / 作品评审 / 入驻+服务包</t>
+          <t>开题组队 / 封闭开发 / 路演决赛 / 入驻礼包 / 一对一看场</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>OPC超级个体社区氛围</t>
+          <t>青年菁英/Builders氛围</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>工具型/服务型小团队入驻</t>
+          <t>获奖团队优先谈单元</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>我方3+园区2</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1">
+          <t>我方5+园区3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="50" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>智能体/多模态/算力训练</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>AI培训 / 黑客松</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>OPC超级个体黑客松（秋季）</t>
+          <t>AI营销Agent实战营</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>9月中旬</t>
+          <t>10月中旬</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>3F整层</t>
+          <t>3F培训</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.5天</t>
+          <t>半天</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>黑客松</t>
+          <t>实战营</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>评委+赞助商+媒体</t>
+          <t>投放操盘手、Agent产品经理</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>同春季结构 / 增加秋季赛道（出海/短剧） / 决赛路演 / 媒体采访 / 集中逼单日</t>
+          <t>投放策略 / Agent自动化 / 素材AIGC / 复盘 / 服务包转化</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>年度品牌IP化第二峰</t>
+          <t>企业服务粘性</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>秋季去化冲刺客源</t>
+          <t>营销型公司入驻</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>我方5+园区3</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1">
+          <t>我方3+园区1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>政策与治理沙龙</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>AI培训 / 黑客松</t>
+          <t>智能伙伴</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>AI营销投放实战营</t>
+          <t>YOUNG立方×智能伙伴政策沙龙</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10月中旬</t>
+          <t>1月中旬</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3F培训</t>
+          <t>5F沙龙</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>半天</t>
+          <t>2.5小时</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>实战营</t>
+          <t>沙龙</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>投放操盘手、品牌主</t>
+          <t>区政策宣讲、服务中心</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>投放策略 / 素材AIGC生产 / 投流复盘 / 园区企业案例 / 增值服务转化</t>
+          <t>政策要点 / WAIC主题与园区礼包 / 适用画像 / 诊断预约 / 看场</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>企业服务增收、会员粘性</t>
+          <t>政策前置+主题统一</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>营销型公司与广告客户</t>
+          <t>内容/AI企业导入</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>我方3+园区1</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="48" customHeight="1">
+          <t>我方2+园区2+服务中心2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>政策与治理沙龙</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>AI培训 / 黑客松</t>
+          <t>治理</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>创智汇AI年度Demo Day</t>
+          <t>AI治理与可信智能体沙龙</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>12月上旬</t>
+          <t>2月下旬</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>5F主展区</t>
+          <t>3F</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1天</t>
+          <t>2小时</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>路演日</t>
+          <t>沙龙</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>投资人、链主、媒体、区级嘉宾</t>
+          <t>治理学者、合规顾问、企业法务</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>开幕致辞 / 十强路演 / 颁奖 / 招商政策发布 / 红酒洽谈+看场</t>
+          <t>全球治理框架速递 / 企业合规清单 / 案例 / 问答 / 入驻服务对接</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>年度成果展、政府可见度</t>
+          <t>呼应WAIC全球AI治理高级别会议</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>集中签约意向、媒体背书</t>
+          <t>合规意识型企业信任入驻</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>我方6+园区4</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="48" customHeight="1">
+          <t>我方2+服务中心2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="50" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>政策与治理沙龙</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>政策沙龙 / 路演</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>YOUNG立方政策解读沙龙</t>
+          <t>高企认定冲刺（AI企业专场）</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1月中旬</t>
+          <t>3月中旬</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5F沙龙区</t>
+          <t>3F</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2.5小时</t>
+          <t>半天</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>沙龙</t>
+          <t>辅导会</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>区政策宣讲人、服务中心</t>
+          <t>高企辅导、财税顾问</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>政策要点 / 适用企业画像 / 申报路径 / 问答 / 诊断预约+看场</t>
+          <t>条件拆解 / AI企业材料要点 / 初筛 / 辅导套餐 / 入驻激励</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>政策礼包前置、载体认知</t>
+          <t>在园资质提升</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>内容/微短剧企业定向导入</t>
+          <t>外区待认定AI企业带政策入驻</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>我方2+园区2+服务中心2</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="48" customHeight="1">
+          <t>我方2+服务中心3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="50" customHeight="1">
       <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>政策与治理沙龙</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>政策沙龙 / 路演</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>高企认定冲刺辅导会</t>
+          <t>专精特新·AI应用培育路演</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>2月下旬</t>
+          <t>6月上旬</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>3F会议室</t>
+          <t>5F</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1346,207 +1311,192 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>辅导会</t>
+          <t>路演</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>高企辅导老师、财税顾问</t>
+          <t>评审顾问、银行、基金</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>条件拆解 / 材料清单 / 失败案例 / 一对一初筛 / 入驻即享辅导套餐</t>
+          <t>梯度政策 / 企业路演 / 点评 / 金融对接 / 看场</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>在园企业资质提升</t>
+          <t>优质企业筛选</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>外区待认定企业「带政策入驻」</t>
+          <t>成长型AI企业补位</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>我方2+服务中心3</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="48" customHeight="1">
+          <t>我方3+园区2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="50" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>政策与治理沙龙</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>政策沙龙 / 路演</t>
+          <t>算力</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>专精特新培育路演</t>
+          <t>创新券·算力券·模型券实务沙龙</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4月上旬</t>
+          <t>11月上旬</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5F</t>
+          <t>3F</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>半天</t>
+          <t>2小时</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>路演</t>
+          <t>实务沙龙</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>专精特新评审顾问、银行</t>
+          <t>创新券平台、云厂商</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>梯度政策 / 企业路演 / 导师点评 / 金融对接 / 看场与意向表</t>
+          <t>三券规则 / 核销实操 / 案例 / 开户引导 / 入驻转化</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>优质企业筛选与培育</t>
+          <t>服务机构KPI与核销流水</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>成长型企业补位招商</t>
+          <t>用券企业向园区聚集</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>我方3+园区2</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="48" customHeight="1">
+          <t>我方2+服务中心2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="50" customHeight="1">
       <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>产业与科学对接</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>政策沙龙 / 路演</t>
+          <t>AI for Science</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>杨浦科创政策一对一诊断日</t>
+          <t>高校成果转化·AI for Science日</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>5月下旬</t>
+          <t>4月中旬</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>3F多间工位</t>
+          <t>3F+沙龙</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1天滚动</t>
+          <t>半天</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>门诊式诊断</t>
+          <t>对接日</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>服务中心顾问团</t>
+          <t>复旦/同济技术转移、教授团队</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>预约排号 / 20分钟/企诊断 / 政策匹配表输出 / 当场报价 / 三日回访逼单</t>
+          <t>成果路演 / 科学智能体场景 / 园区承接方案 / 看孵化单元 / 转化落位</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>服务中心专业形象</t>
+          <t>对齐WAICA科学多模态/AI for Science</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>高意向客户集中转化</t>
+          <t>成果公司/实验室落户</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>我方3+服务中心4+园区1</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="48" customHeight="1">
+          <t>我方3+园区2+高校2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="50" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>产业与科学对接</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>政策沙龙 / 路演</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>投融资对接路演（AI赛道）</t>
+          <t>汕头玩具×AIGC供应链对接会</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7月中旬</t>
+          <t>4月下旬</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5F</t>
+          <t>5F玩具区</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1556,137 +1506,127 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>路演+闭门</t>
+          <t>对接会</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>基金×5、明星项目×8</t>
+          <t>汕头商协会、品牌采购</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>项目路演 / 闭门对接 / 园区资本资源介绍 / 入驻条件 / 投资+租赁联动</t>
+          <t>集群介绍 / AIGC设计提效 / 供需对接 / 展位参观 / 报价</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>资本氛围、优质项目落位</t>
+          <t>5F集群填充+AI赋能传统产业</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>获投项目优先谈租金/免租</t>
+          <t>玩具企业展位去化</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>我方4+园区2</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="48" customHeight="1">
+          <t>我方3+园区2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="50" customHeight="1">
       <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>产业与科学对接</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>政策沙龙 / 路演</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>创新券·三券申用实务沙龙</t>
+          <t>扬州毛绒×数字人联名对接</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>11月上旬</t>
+          <t>6月中旬</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>5F毛绒区</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2小时</t>
+          <t>半天</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>实务沙龙</t>
+          <t>对接会</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>创新券平台、云厂商</t>
+          <t>扬州集群、数字人厂商</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>券种规则 / 核销实操 / 案例 / 服务机构对接 / 入驻企业开户引导</t>
+          <t>联名模式 / 租金/扣点测算 / 看场 / MOU / 跟进</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>创新券流水、服务机构KPI</t>
+          <t>毛绒集群落地</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>需用券企业向园区聚集</t>
+          <t>700㎡量级客户</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>我方2+服务中心2</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="48" customHeight="1">
+          <t>我方3+园区2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="50" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>产业与科学对接</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>行业对接 / 撮合</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>汕头玩具供应链对接会</t>
+          <t>东莞潮玩品牌入沪推介</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3月中旬</t>
+          <t>8月上旬</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5F玩具集群区</t>
+          <t>5F潮玩区</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1696,27 +1636,27 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>对接会</t>
+          <t>推介会</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>汕头商协会、品牌采购</t>
+          <t>潮玩品牌、渠道商</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>集群介绍 / 供需对接 / 展位参观 / 意向签约墙 / 展位/仓储报价</t>
+          <t>上海渠道 / 5F落位 / 联名活动 / 看场 / 定金意向</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5F产业集群填充</t>
+          <t>潮玩内容填充</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>玩具企业展位去化</t>
+          <t>品牌展位/快闪</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -1724,804 +1664,744 @@
           <t>我方3+园区2</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="48" customHeight="1">
+    </row>
+    <row r="19" ht="50" customHeight="1">
       <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>产业与科学对接</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>行业对接 / 撮合</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>扬州毛绒产业游学对接</t>
+          <t>IP授权×AI衍生交易撮合会</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>4月下旬</t>
+          <t>9月中旬</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>5F+外部游学</t>
+          <t>5F展示中心</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1天（含半天园内）</t>
+          <t>1天</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>游学对接</t>
+          <t>撮合会</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>扬州产业集群代表</t>
+          <t>IP方、被授权商、律师</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>园内展区介绍 / 合作模式（租金/扣点） / 游学小结 / 入驻MOU / 跟进清单</t>
+          <t>IP路演 / AI衍生专题桌 / 一对一撮合 / 成交看板 / 落户激励</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>毛绒集群落地</t>
+          <t>IP交易+AI衍生</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>700㎡量级客户</t>
+          <t>IP/衍生品团队入驻</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>我方3+园区2</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="48" customHeight="1">
+          <t>我方4+园区2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="50" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AI内容与IP</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>行业对接 / 撮合</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东莞潮玩品牌入沪推介</t>
+          <t>AI创作者内容首发①</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6月上旬</t>
+          <t>5月下旬</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5F潮玩区</t>
+          <t>5F主展</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>半天</t>
+          <t>3小时</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>推介会</t>
+          <t>发布会</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>潮玩品牌方、渠道商</t>
+          <t>创作者、媒体、渠道</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>上海渠道机会 / 5F落位方案 / 联名活动设想 / 看场 / 定金/意向</t>
+          <t>揭幕 / 发布 / 签售快闪 / 媒体专访 / 招商通道</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>潮玩内容填充</t>
+          <t>与官方创作者之夜错位：园区做「可落位」首发</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>品牌展位与快闪</t>
+          <t>关联品牌问询</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>我方3+园区2</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="48" customHeight="1">
+          <t>我方4+园区3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="50" customHeight="1">
       <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AI内容与IP</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>行业对接 / 撮合</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>IP授权交易撮合会</t>
+          <t>潮玩×AIGC主题市集</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>7月下旬</t>
+          <t>6月下旬</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>5F展示中心</t>
+          <t>5F+公区</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1天</t>
+          <t>2天</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>撮合会</t>
+          <t>市集</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>IP方、被授权商、律师</t>
+          <t>摊主×40、达人</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>IP路演 / 一对一撮合桌 / 法律速递 / 成交看板 / 落户激励</t>
+          <t>布摊 / 开市 / AIGC互动打卡 / 夜间场 / 优质摊主转正谈</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>IP交易氛围、分成收入</t>
+          <t>人气与经营收入</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>IP公司与衍生品团队入驻</t>
+          <t>摊主升级固定展位/办公</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>我方4+园区2</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="48" customHeight="1">
+          <t>我方5+园区4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="50" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AI内容与IP</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>行业对接 / 撮合</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>高校成果转化对接日</t>
+          <t>沉浸式AI+IP联展</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9月下旬</t>
+          <t>8月中旬</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3F+沙龙</t>
+          <t>5F展示中心</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>半天</t>
+          <t>7–10天</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>对接日</t>
+          <t>联展</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>复旦/同济技术转移、教授团队</t>
+          <t>联合IP×5、文旅渠道</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>成果路演 / 中试/场景需求 / 园区承接方案 / 看孵化单元 / 转化落位协议</t>
+          <t>布展 / 开幕 / 预约观展 / 教育场 / 闭幕招商酒会</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>高校协同、学术支持落地</t>
+          <t>长期人流</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>成果公司/实验室落户</t>
+          <t>闭幕酒会集中转化</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>我方3+园区2+高校2</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="48" customHeight="1">
+          <t>我方4+园区3+外包</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="50" customHeight="1">
       <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AI内容与IP</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>行业对接 / 撮合</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>跨境展销买家对接会</t>
+          <t>AI创作者内容首发②</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>11月中旬</t>
+          <t>10月下旬</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>5F展贸</t>
+          <t>5F</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>半天</t>
+          <t>3小时</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>买家对接</t>
+          <t>发布会</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>跨境买家、货代、支付机构</t>
+          <t>IP方、渠道、媒体</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>买家需求发布 / 供应商闪见 / 展位下单 / 物流金融配套 / 展贸租户转化</t>
+          <t>发布 / 双十一预售 / 渠道对接 / 看场 / 年框意向</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>5F贸易属性兑现</t>
+          <t>下半年内容高峰</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>外贸/跨境团队办公+展位</t>
+          <t>旺季补位</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>我方4+园区2</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="48" customHeight="1">
+          <t>我方4+园区3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="50" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>WAIC联动大场</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>IP / 潮玩活动</t>
+          <t>WAIC主会</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>IP首发发布会①</t>
+          <t>WAIC UP! 创智汇「智能伙伴」开放日</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5月中旬</t>
+          <t>7月17日</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5F主展</t>
+          <t>3F+5F整区</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3小时</t>
+          <t>1天（10:00–17:00）</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>发布会</t>
+          <t>开放日</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>IP主理人、媒体、渠道</t>
+          <t>参展回流嘉宾、媒体、企业、高校</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>揭幕 / 发布会 / 签售/快闪 / 媒体专访 / 招商通道开放</t>
+          <t>10:00 开幕致辞（联合会+同浦汇） / 10:30 WAIC主题速递与园区承接 / 11:30 空间开放参观 / 14:00 Agent/内容双展台 / 15:30 政策礼包发布 / 16:30 意向洽谈</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>内容事件、客流</t>
+          <t>WAIC日间散场承接、杨浦可见度</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>关联品牌问询与展位</t>
+          <t>大会流量导入园区看场</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>我方4+园区3</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="48" customHeight="1">
+          <t>我方6+园区5+服务中心2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="50" customHeight="1">
       <c r="A25" s="3" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>WAIC联动大场</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>IP / 潮玩活动</t>
+          <t>Builders夜</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>潮玩主题周末市集</t>
+          <t>WAIC UP! AI Builders Night·建造者之夜</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>6月下旬</t>
+          <t>7月17日晚</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>5F+公区</t>
+          <t>5F主厅+露台/沙龙</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2天</t>
+          <t>18:30–21:30</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>市集</t>
+          <t>夜场社交</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>摊主×40、达人</t>
+          <t>创业者、开发者、投资人、开源Maintainer</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>摊位布置 / 开市 / 互动打卡 / 夜间场 / 优质摊主转正谈</t>
+          <t>18:30 签到·名牌「我正在造的AI」 / 18:40 致辞 / 18:50 闪电演讲×4 / 19:40 1分钟开放麦 / 20:10 AMA / 20:40 投资人蹲项目区+看场</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>人气、经营性收入</t>
+          <t>对齐北外滩双夜Day1逻辑，落位创智汇</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>摊主升级为固定展位/办公</t>
+          <t>建造者当场看3F单元</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>我方5+园区4</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="48" customHeight="1">
+          <t>我方5+园区3+联合会2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="50" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>WAIC联动大场</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>IP / 潮玩活动</t>
+          <t>AGI夜</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>沉浸式IP联展</t>
+          <t>WAIC UP! 通往AGI之夜</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8月中旬</t>
+          <t>7月18日晚</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5F展示中心</t>
+          <t>5F圆桌+学术酒吧分区</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>7–10天巡展</t>
+          <t>19:00–21:30</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>联展</t>
+          <t>学术夜场</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>联合IP×5、文旅渠道</t>
+          <t>复旦学者、大模型负责人、Agent创始人、治理学者</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>布展 / 开幕礼 / 预约观展 / 教育场 / 闭幕招商酒会</t>
+          <t>19:00 复旦致辞定调 / 19:10 无PPT圆桌：通往AGI走到哪了 / 20:10 三桌围炉（模型/智能体/科学与治理） / 20:40 辩题投票 / 21:00 深度社交+精品看场</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>长期人流、品牌形象</t>
+          <t>对齐WAICA思辨+复旦学术支持</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>闭幕酒会集中转化</t>
+          <t>高端涉外/研究型企业入驻</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>我方4+园区3+执行外包</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="48" customHeight="1">
+          <t>我方4+园区2+复旦2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="50" customHeight="1">
       <c r="A27" s="3" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>WAIC联动大场</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>IP / 潮玩活动</t>
+          <t>青年菁英</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>IP首发发布会②</t>
+          <t>创智汇秋季潮玩×AI嘉年华</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>10月下旬</t>
+          <t>10月上旬</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>5F</t>
+          <t>5F+公区</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>3小时</t>
+          <t>2天</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>发布会</t>
+          <t>嘉年华</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>IP方、玩具渠道、媒体</t>
+          <t>潮玩品牌、达人、赞助商、AI创作者</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>同①结构 / 叠加双十一预售 / 渠道对接 / 看场 / 年框意向</t>
+          <t>开幕秀 / 市集+展洽 / AI互动赛事 / 夜间场 / 签约仪式</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>下半年内容高峰</t>
+          <t>秋季品牌大事件、WAIC精神延续</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>旺季补位招商</t>
+          <t>集中签约展位/办公</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>我方4+园区3</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="48" customHeight="1">
+          <t>我方8+园区6+外包</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="50" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>出海/AGI/收官</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>漫展 / 大型活动</t>
+          <t>出海</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>创智汇春季漫展</t>
+          <t>AI出海推介与国际买家团</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4月下旬</t>
+          <t>9月下旬</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5F+可临建</t>
+          <t>5F+培训</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2天</t>
+          <t>1天</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>漫展</t>
+          <t>买家团</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Coser、品牌商、媒体、赞助商</t>
+          <t>海外买家、跨境平台、出海顾问</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>开幕 / 舞台演出 / 展商区 / 门票核销 / 闭幕+企业招商通道</t>
+          <t>出海路径 / 买家需求 / 一对一洽谈 / 订单意向 / 办公/展位捆绑</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>千人级声量、门票赞助收入、载体KPI</t>
+          <t>出海服务闭环</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>展商/品牌方留资转租赁</t>
+          <t>出海需求企业入驻</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>我方8+园区6+安保票务外包</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="48" customHeight="1">
+          <t>我方5+园区2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="50" customHeight="1">
       <c r="A29" s="3" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>出海/AGI/收官</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>漫展 / 大型活动</t>
+          <t>AGI</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>创智汇秋季潮玩嘉年华</t>
+          <t>通往AGI季度圆桌①</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>10月上旬</t>
+          <t>4月下旬</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>5F+公区</t>
+          <t>5F沙龙</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2天</t>
+          <t>2.5小时</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>嘉年华</t>
+          <t>圆桌</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>潮玩品牌、达人、赞助商</t>
+          <t>学者、模型企业、投资人</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>开幕秀 / 市集+展洽 / 赛事 / 夜间场 / 嘉年华签约仪式</t>
+          <t>议题导入 / 圆桌 / 围炉 / 问答 / 看场</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>秋季品牌大事件</t>
+          <t>AGI议题全年运营（WAIC会后延续）</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>集中签约展位/办公</t>
+          <t>研究型/模型团队</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>我方8+园区6+外包</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="48" customHeight="1">
+          <t>我方3+园区1+学术1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="50" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>出海/AGI/收官</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>领事 / 出海</t>
+          <t>领事</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>国别会客厅·领事专题沙龙</t>
+          <t>国别会客厅·AI合作领事专题</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5月下旬</t>
+          <t>11月中旬</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2541,62 +2421,57 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>领事官员、涉外企业、翻译</t>
+          <t>领事官员、涉外AI企业、翻译</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>外事礼仪接待 / 国别机会分享 / B2B闪见 / 园区国际服务介绍 / 高端看场</t>
+          <t>外事接待 / 国别AI机会 / B2B闪见 / 国际服务介绍 / 高端看场</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>高端背书、国际形象</t>
+          <t>国际背书</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>涉外/出海企业入驻</t>
+          <t>涉外/出海企业</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>我方4+园区2+外事协同</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="48" customHeight="1">
+          <t>我方4+园区2+外事</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="50" customHeight="1">
       <c r="A31" s="3" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>出海/AGI/收官</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>领事 / 出海</t>
+          <t>智能伙伴</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>企业出海推介与买家团</t>
+          <t>创智汇AI年度Demo Day·智能伙伴收官</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>11月下旬</t>
+          <t>12月上旬</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>5F+培训</t>
+          <t>5F主展</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2606,37 +2481,32 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>推介+买家团</t>
+          <t>路演日</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>海外买家、跨境平台、出海顾问</t>
+          <t>投资人、链主、媒体、区级嘉宾</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>出海路径课 / 买家需求 / 一对一洽谈 / 订单意向 / 办公/展位捆绑</t>
+          <t>开幕 / 十强路演 / 颁奖 / 明年WAIC预热 / 红酒洽谈+集中签约</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>出海服务闭环、撮合收入</t>
+          <t>年度成果+来年WAIC预热</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>有出海需求的制造/品牌入驻</t>
+          <t>集中签约与媒体背书</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>我方5+园区2</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>场中看场+意向表；T+1~7回访逼单</t>
+          <t>我方6+园区4</t>
         </is>
       </c>
     </row>
@@ -2651,144 +2521,246 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>环节</t>
+          <t>项目</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>动作</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>园区协同</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>成功标准</t>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>大会主题</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>智能伙伴 共创未来</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>2026.7.17–7.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>地点</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>浦东世博 · 张江 · 徐汇西岸「三地四馆」</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>学术板块</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>WAICA 7.18–7.20：主会报告 + 科学多模态智能体 / 数学建模 / 天基智能计算 / 量子加速 / 具身智能 / 青年菁英会</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>夜场逻辑参考</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Builders Night（暖身社交）→ 通往AGI之夜（深度思辨）；创智汇7.17–7.18落地</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>园区角色</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>杨浦承接会客厅：大会流量日间承接 + 夜场深度转化 + 全年赛道常态化</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>时段</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>议程</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>创智汇可借势</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>活动前</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>名单筛选、邀约、礼包预热</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>共享在谈客户、确认场地物业</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>到会名单锁定</t>
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>7.18</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>09:00–12:00</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>WAICA开幕式</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>开放日预热/接驳</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>活动中</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>签到建档、看场、意向表、限时礼</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>1–6人现场支持（按场次）</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>留资率≥60%</t>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>7.18</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>14:00–17:00</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>主会技术报告1（最佳论文/Agent等）</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Builders Night议题素材</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>会后7日</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>回访、报价、二次看场</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>会议室/决策人对接</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>看场率≥25%</t>
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>09:00–12:00</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>科学多模态智能体 / 数学建模与科学计算工作坊</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>AI for Science对接日话术</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>成交</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>合同、入驻、申报接棒</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>合同与物业交割</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>月度签约看板</t>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>14:00–17:00</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>天基智能计算·智能体 / 量子计算加速</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>算力Infra实务营内容</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>复盘反哺</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>ROI与漏斗优化</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>月度联席会</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>下场转化提升</t>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>7.20</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>09:00–12:00</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>主会4–6 + 具身智能空间交互 + 青年菁英会</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>具身体验日/青年黑客松</t>
         </is>
       </c>
     </row>

--- a/proposal/创智汇30场活动方案排期表.xlsx
+++ b/proposal/创智汇30场活动方案排期表.xlsx
@@ -8,8 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01-活动概况" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02-主体分工收费付款" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03-往期案例" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02-定义核资源导入" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03-双会资源摘要" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04-主体分工收费付款" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05-往期案例" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06-层次叠加说明" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -458,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -467,12 +470,13 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -513,25 +517,30 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>节奏</t>
+          <t>层次</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>资源源</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>价值落点</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>行程</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>嘉宾</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>交付</t>
         </is>
@@ -575,25 +584,30 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>T-14物料→T-7邀约→T-1彩排→D日→建群回访</t>
+          <t>L0点火</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>园区自建</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>中介渠道带看与项目推介</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>项目介绍→空间导览→政策要点→一对一洽谈→建群</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>房产/产业中介、渠道机构、园区招商同事</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>方案+议程+签到+意向表+建群+回访摘要+复盘</t>
         </is>
@@ -637,25 +651,30 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L0点火</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
+          <t>园区自建+投研交叉</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>金融资源链接与企业客户导入</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>项目路演→金融产品对接→企业需求座谈→看场→建群</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>五大行及合作金融机构对公/科创条线</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -699,25 +718,30 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L0点火</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>园区自建</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>投研视角放大项目影响力</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>项目定位→产业赛道研判→圆桌→看场→建群</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>券商研究所、产业研究院、智库分析师</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -761,25 +785,30 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L0点火</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
+          <t>云创基地+科企联/服中心</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <t>政策与载体协同落地</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>载体介绍→政策协同→云创基地资源→看场→建群</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>区相关部门、载体代表、云创基地、服中心</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -823,25 +852,30 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L1双会承接</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>WAIC总表</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>衔接WAIC议题与园区看场</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>WAIC议题速递→园区承接→双展台→洽谈→建群</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>AI/内容企业、媒体、云创基地代表</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>同上+通稿</t>
         </is>
@@ -885,25 +919,30 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·3F能力</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
+          <t>WAIC·大模型/Agent</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
           <t>Agent初创落位</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>签到→工作流→实操→Demo→看场</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>Agent工程师、初创团队</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -947,25 +986,30 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·5F内容</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>CJ·游戏风云/IP</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>ChinaJoy赛道企业/IP方入驻与展位</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>ChinaJoy赛道解读→IP授权→一对一撮合→看场→建群</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>游戏/动漫/潮玩IP方、渠道、内容公司</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1009,25 +1053,30 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>立项后单独排期</t>
+          <t>另计价</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
+          <t>CJ·国际展团（另案）</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
           <t>出海需求企业服务（不在年度活动包费用内）</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>另案确定</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>另案确定</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>另案合同与交付清单</t>
         </is>
@@ -1071,25 +1120,30 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·3F能力</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>WAIC·多模态/AIGC</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>多模态团队入驻</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>案例→实操→共创→评审→看场</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>多模态应用团队、产品负责人</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1133,25 +1187,30 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·5F内容</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
+          <t>CJ·游戏风云</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
           <t>ChinaJoy生态企业集中看场与洽谈</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>开幕→赛道分享→展洽→看场→建群</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>数字娱乐企业、内容工作室、渠道</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1195,25 +1254,30 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·3F能力</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>WAIC·治理标准论坛</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>合规型企业信任导入</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>治理框架→合规清单→案例→问答→对接</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>合规顾问、企业法务/负责人</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1257,25 +1321,30 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·3F能力</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
+          <t>WAIC·算力/芯片 + CJ云服务示例</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
           <t>高算力企业定向看场</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>政策包→代金券→案例→诊断→看场</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>火山引擎、云创基地、企业技术负责人</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1319,25 +1388,30 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·3F能力</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>云创+WAIC算力池</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>用券企业聚集</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>三券规则→核销→案例→开户→入驻洽谈</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>券平台、云厂商、企业负责人</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1381,25 +1455,30 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>外事流程单独排期</t>
+          <t>另计价</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
+          <t>另案</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
           <t>领事到访接待（不在三部分活动费用内）</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>另案确定</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>领事及相关方（另案）</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>另案报价与执行方案</t>
         </is>
@@ -1443,25 +1522,30 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L3叠加</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>WAIC具身 + CJ Vision Future</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>具身/机器人团队看场</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>演示→讲解→场景→踩点→洽谈</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>具身团队、高校实验室</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1505,25 +1589,30 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L4收口</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
+          <t>双会精选项目</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
           <t>集中签约洽谈与媒体背书</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>开幕→精选路演→颁奖→洽谈</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>投资人、链主、媒体、精选项目</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>同上+签约台账</t>
         </is>
@@ -1567,25 +1656,30 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·5F内容</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>WAIC·内容创意AIGC</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>厂牌/工作室入驻</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>政策→制片→脚本→路演→看场</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>导演、厂牌、平台方</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1629,25 +1723,30 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·3F能力</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
+          <t>WAIC·企业服务与营销</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
           <t>营销科技公司看场</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>策略→Agent→素材→复盘→转化</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>投放操盘手、产品经理</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1691,25 +1790,30 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·政策</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>服中心+双会客群</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>内容/AI企业导入</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>政策→礼包→画像→诊断→看场</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>政策宣讲、服中心、企业负责人</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1753,25 +1857,30 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·政策</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
+          <t>服中心</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
           <t>待认定企业带政策入驻</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>条件→材料→初筛→套餐→激励</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>辅导顾问、待认定企业负责人</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1815,25 +1924,30 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·3F能力</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>WAIC·青年/OPC + CJ创作者</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>获奖团队优先谈单元</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>开题→开发→路演→礼包→看场</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>评委、投资人、Builders</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1877,25 +1991,30 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·学术</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
+          <t>学术支持+WAIC科研赛道</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
           <t>成果公司/实验室落户</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>成果路演→场景→承接→看单元→洽谈</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>复旦/同济技转、教授团队、住房政策研究中心学者（学术支持）</t>
         </is>
       </c>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="M23" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1939,25 +2058,30 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·3F能力</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>WAIC·大模型论坛</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>研究型/模型团队</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>议题→圆桌→围炉→问答→看场</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>学者、模型企业、投资人</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -2001,25 +2125,30 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·5F内容</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
+          <t>CJ·创作者展区</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
           <t>数字娱乐/内容品牌问询</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>揭幕→发布→快闪→专访→招商通道</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>创作者、媒体、渠道、ChinaJoy相关内容方</t>
         </is>
       </c>
-      <c r="L25" s="3" t="inlineStr">
+      <c r="M25" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -2063,25 +2192,30 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·5F内容</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>CJ·魔玩/谷子</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>ChinaJoy供应链/周边企业展位落位</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>赛道介绍→供需对接→展位参观→报价→建群</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>游戏周边、潮玩供应链、渠道采购</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -2125,25 +2259,30 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·3F能力</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
+          <t>WAIC·行业AI + ACT-006</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
           <t>成长型AI补位</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>政策→路演→点评→金融→看场</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t>顾问、银行、基金、企业</t>
         </is>
       </c>
-      <c r="L27" s="3" t="inlineStr">
+      <c r="M27" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -2187,25 +2326,30 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·5F内容</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>CJ·创作者/市集形态</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>优质摊主/工作室升级固定展位</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>布展→体验→交流→转正洽谈→建群</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>内容工作室、周边品牌、达人</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -2249,25 +2393,30 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·5F内容</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
+          <t>CJ·IP/联名</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
           <t>IP联名/衍生品团队入驻</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>IP路演→联名模式→一对一→MOU→看场</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="L29" s="3" t="inlineStr">
         <is>
           <t>IP方、衍生品商、渠道</t>
         </is>
       </c>
-      <c r="L29" s="3" t="inlineStr">
+      <c r="M29" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -2311,25 +2460,30 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>展期预约制</t>
+          <t>L2·5F内容</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
+          <t>CJ·氛围落地</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>闭幕洽谈集中转化</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>布展→预约观展→交流→闭幕洽谈</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>联合内容方、渠道、品牌</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -2373,25 +2527,30 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L4收口/预热</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
+          <t>双会预热</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
           <t>旺季补位，双大会预热</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>发布→渠道→看场→年框→双会预热</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
+      <c r="L31" s="3" t="inlineStr">
         <is>
           <t>IP方、渠道、媒体</t>
         </is>
       </c>
-      <c r="L31" s="3" t="inlineStr">
+      <c r="M31" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -2408,7 +2567,1461 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>活动名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>层次</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>定义核</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>资源源</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>资源导入（招商向）</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>价值落点</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>创智汇项目推广日①·中介与渠道专场</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>L0点火</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>渠道点火场：把「AI+数字内容共创港」讲清楚，导入后续带客池</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>园区自建</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>双会客群转介话术包；待租8间看场清单</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>中介渠道带看与项目推介</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="52" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>创智汇项目推广日②·五大行与金融机构专场</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>L0点火</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>金融转介场：用科创金融话术放大带客可信度</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>园区自建+投研交叉</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>WAIC金融科技论坛议题摘要；CJ BTOB专业观众画像</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>金融资源链接与企业客户导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>创智汇项目推广日③·投研机构专场</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>L0点火</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>叙事定调场：对外统一园区赛道故事</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>园区自建</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>WAIC赛道结论（大模型/具身/算力）；CJ「与AI同游」产业判断</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>投研视角放大项目影响力</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>创智汇项目推广日④·政府部门与载体协同专场</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>L0点火</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>政策协同场：主体背书与载体资源上桌</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>云创基地+科企联/服中心</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>云创算力券/创新券口径；YOUNG立方政策包</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>政策与载体协同落地</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>WAIC成果承接·创智汇开放交流日</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>L1双会承接</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>WAIC余热承接：把大会议题压缩为园区可看场的≤30人交流</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>WAIC总表</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>A/B线索抽样邀约；ACT-001/002/006议题切片；不堆全量963展商</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>衔接WAIC议题与园区看场</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Agent智能体搭建一日营</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>L2·3F能力</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>3F入孵核：Agent能力→OPC工位转化</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>WAIC·大模型/Agent</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>WAIC行业：AI Agent约87家池；ACT-001闭门会缩尺</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Agent初创落位</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>ChinaJoy主题·数字娱乐与IP授权对接会</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>L2·5F内容</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5F内容核：IP授权对接→展位/办公问询</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>CJ·游戏风云/IP</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>CJ优先：中小工作室+IP授权方；可触达263抽样，不追大厂总部</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>ChinaJoy赛道企业/IP方入驻与展位</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>出海专题活动（另议·另计价）</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>另计价</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>另议核：出海不进年度包，另案另计价</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>CJ·国际展团（另案）</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>CJ BTOB外资线索仅作另案素材；本册不承诺外企到场</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>出海需求企业服务（不在年度活动包费用内）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>多模态智能体工作坊</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>L2·3F能力</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3F技术核：多模态团队看场入驻</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>WAIC·多模态/AIGC</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>WAIC AIGC图像/视频/3D子类抽样；论坛「内容创意与AIGC」切片</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>多模态团队入驻</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>ChinaJoy主题日·数字娱乐生态交流</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>L2·5F内容</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>5F生态核：数字娱乐集中看场</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>CJ·游戏风云</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Express/独立游戏中小团队池；库洛/鹰角/散爆等仅作赛道示例非名单承诺</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>ChinaJoy生态企业集中看场与洽谈</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>AI治理与可信智能体沙龙</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>L2·3F能力</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>信任核：治理合规降低入驻决策摩擦</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>WAIC·治理标准论坛</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>WAIC治理赛道7场论坛议题摘要；合规顾问短名单</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>合规型企业信任导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>火山引擎×算力Infra实务营</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>L2·3F能力</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>算力核：云创基地×厂商联训→高算力看场</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>WAIC·算力/芯片 + CJ云服务示例</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>ACT-003缩尺；WAIC算力展商226家池抽样；云创算力资源</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>高算力企业定向看场</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>创新券·算力券·模型券实务沙龙</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>L2·3F能力</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>券务核：用券企业聚集转化</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>云创+WAIC算力池</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>三券核销路径；WAIC算力/云厂商联系人抽样</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>用券企业聚集</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>领事到访接待（另计价）</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>另计价</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>外事另计价核：到访≠挂牌，分开报价</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>另案</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>不占用年度30场资源池</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>领事到访接待（不在三部分活动费用内）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>具身智能空间交互体验日</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>L3叠加</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>双会叠加核：具身体验→3F/5F联合看场</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>WAIC具身 + CJ Vision Future</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>ACT-002缩尺；WAIC场景观察（零售/工业物流）；CJ前沿科技高优先级</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>具身/机器人团队看场</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>创智汇AI年度Demo Day</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>L4收口</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>年中收口核：精选项目集中签约洽谈</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>双会精选项目</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>年内WAIC/CJ导入的A/B意向项目精选路演，不做全量路演</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>集中签约洽谈与媒体背书</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>AIGC微短剧制片特训</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>L2·5F内容</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>内容制片核：微短剧厂牌→5F展陈/3F办公</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>WAIC·内容创意AIGC</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>WAIC「AI赋能影视内容」论坛切片；AIGC厂牌抽样</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>厂牌/工作室入驻</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>AI营销Agent实战营</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>L2·3F能力</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>营销科技核：投放团队看场入驻</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>WAIC·企业服务与营销</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>WAIC企业服务/营销86家池抽样；Agent应用团队</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>营销科技公司看场</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>YOUNG立方×智能伙伴政策沙龙</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>L2·政策</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>政策获客核：YOUNG立方礼包转化</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>服中心+双会客群</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>政策礼包+双会导入意向企业复邀</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>内容/AI企业导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>高企认定冲刺（AI企业专场）</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>L2·政策</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>带政策入驻核：高企辅导绑定入驻套餐</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>服中心</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>双会AI应用类待认定企业名单抽样</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>待认定企业带政策入驻</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>OPC超级个体黑客松（春）</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>L2·3F能力</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>OPC核：黑客松获奖→优先谈单元</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>WAIC·青年/OPC + CJ创作者</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>高校/青年Builder；CJ AGS高校团队线索抽样</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>获奖团队优先谈单元</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>高校成果转化·AI for Science日</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>L2·学术</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>成果转化核：高校实验室/公司落户</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>学术支持+WAIC科研赛道</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>复旦住房政策研究中心学术支持位；WAIC前沿科研论坛切片</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>成果公司/实验室落户</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>通往AGI季度圆桌</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>L2·3F能力</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>研究型客户核：闭门圆桌深谈看场</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>WAIC·大模型论坛</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>ACT-001闭门形态；模型公司抽样（不作全量邀约）</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>研究型/模型团队</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>ChinaJoy主题·创作者内容首发①</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>L2·5F内容</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>创作者首发核：内容发布带招商通道</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>CJ·创作者展区</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>CJ创作者/社团抽样；渠道复用（抖音/小红书玩法迁移园区）</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>数字娱乐/内容品牌问询</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>ChinaJoy主题·游戏周边与潮玩供应链对接</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>L2·5F内容</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>供应链核：周边/潮玩→5F展位落位</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>CJ·魔玩/谷子</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>CJ潮玩谷子高优先级；JOYTOY/卡游等仅作品类示例</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>ChinaJoy供应链/周边企业展位落位</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>专精特新·AI应用培育路演</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>L2·3F能力</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>成长补位核：专精特新AI应用看场</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>WAIC·行业AI + ACT-006</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>ACT-006案例圆桌缩尺；行业AI114家池抽样</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>成长型AI补位</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>ChinaJoy主题·数字娱乐市集体验日</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>L2·5F内容</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>市集转化核：摊主升级固定展位</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>CJ·创作者/市集形态</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>CJ创作者展区小微品牌；市集→固定展位升级路径</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>优质摊主/工作室升级固定展位</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>ChinaJoy主题·IP联名与衍生品撮合会</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>L2·5F内容</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>IP商业化核：联名撮合→入驻/展位</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>CJ·IP/联名</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>CJ老字号×IP联名案例迁移；衍生品商抽样</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>IP联名/衍生品团队入驻</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="52" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>ChinaJoy主题·沉浸式数字娱乐联展</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>L2·5F内容</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>视觉落地核：短展期氛围→闭幕洽谈</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>CJ·氛围落地</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>联合内容方短名单；预约制控流≤30人/场</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>闭幕洽谈集中转化</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="52" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>创作者首发②·衔接WAIC2027与ChinaJoy</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>L4收口/预热</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>双会预热核：创作者首发衔接下一年双会</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>双会预热</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>全年双会导入线索复盘；预热WAIC2027+下届CJ</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>旺季补位，双大会预热</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>会展</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>指标/策略</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>招商用法</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>映射场次</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>WAIC</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>参展商963 · 品牌主库4262 · 联系人3463 · A/B线索500 · 论坛175</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>A/B线索抽样+议题缩尺，不粘贴全库</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>E1/A2/A3/A4/A5/B2/B4/C4/F3/F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>WAIC</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>ACT-001 大模型闭门</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>缩尺为≤30人 Agent/圆桌</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>A2/A3/F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>WAIC</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>ACT-002 机器人体验供需</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>体验日+看场</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>A5/E1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>WAIC</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>ACT-003 算力芯片峰会</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>厂商联训+券务</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>A4/B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>WAIC</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>ACT-006 行业AI案例</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>路演/政策沙龙</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>C4/B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>ChinaJoy</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>近900家参展 · 可触达优先263 · 精编422 · 主题与AI同游</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>可触达263优先外呼抽样</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>C1/E4/D2/C3/D3/C5/D4/D5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ChinaJoy</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>最高：中小游戏工作室</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Express/Next Play/AGS 孵化向</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>C1/E4/D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>ChinaJoy</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>高：具身 Vision Future</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>与WAIC具身叠加</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>A5/E1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ChinaJoy</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>高：潮玩谷子供应链</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>5F展位/市集转正</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>C3/D3/C5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>ChinaJoy</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>中高：创作者经济</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>首发+渠道复用</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>D2/D5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>原则</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>中腰部灵活/不追大厂总部</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>双会是资源库，30场是定义核</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>全册</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2615,7 +4228,19 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>活动同步衔接 WAIC 与 ChinaJoy</t>
+          <t>WAIC→3F能力线；ChinaJoy→5F内容线；具身/AIGC为叠加带</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>资源原则</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>双会总表只取招商贴近切片；不做全量名单堆砌</t>
         </is>
       </c>
     </row>
@@ -2624,7 +4249,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2756,4 +4381,178 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>层次</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>作用</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>主要来源</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>对应场次</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>L0 点火</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>渠道/金融/投研/政府点火</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>园区自建+载体</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>P1–P4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>L1 双会承接</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>大会余热→园区看场</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>WAIC成果切片</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>L2 楼层主线</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>3F能力 / 5F内容分轨</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>WAIC赛道 + CJ优先策略</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>A/B 与 C/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>L3 双会叠加带</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>具身+AIGC跨楼层</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>WAIC具身×CJ Vision Future</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>A5 等</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>L4 收口/预热</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>签约收口与下届预热</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>年内导入精选</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>F4 / D5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>另计价</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>出海/领事不进年度包</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>另案</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>F1 / L1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/proposal/创智汇30场活动方案排期表.xlsx
+++ b/proposal/创智汇30场活动方案排期表.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>适度承兑约50%，不做100%承诺</t>
+          <t>≤30%</t>
         </is>
       </c>
     </row>
